--- a/excel/TradeMind_LoadTest_500_Report.xlsx
+++ b/excel/TradeMind_LoadTest_500_Report.xlsx
@@ -74,7 +74,7 @@
     <t>Report Timestamp</t>
   </si>
   <si>
-    <t>2026-07-31T05:05:16.825Z</t>
+    <t>2026-07-31T05:17:35.912Z</t>
   </si>
   <si>
     <t>Module Name</t>
